--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/1.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/1.xlsx
@@ -426,13 +426,13 @@
         <v>-2.930848979341327</v>
       </c>
       <c r="E2">
-        <v>-6.613846353933305</v>
+        <v>-10.46054652977818</v>
       </c>
       <c r="F2">
-        <v>1.384038594452115</v>
+        <v>0.8767116055467798</v>
       </c>
       <c r="G2">
-        <v>-13.98591487510026</v>
+        <v>-15.18904127486283</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.441045159788469</v>
       </c>
       <c r="E3">
-        <v>-6.601677444751558</v>
+        <v>-11.24218920753356</v>
       </c>
       <c r="F3">
-        <v>1.933537767833972</v>
+        <v>0.8746092090784746</v>
       </c>
       <c r="G3">
-        <v>-12.20498892541085</v>
+        <v>-14.26907101196322</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.01143214740166</v>
       </c>
       <c r="E4">
-        <v>-7.845161375039197</v>
+        <v>-11.63990072399914</v>
       </c>
       <c r="F4">
-        <v>1.37238180835992</v>
+        <v>1.082434993297231</v>
       </c>
       <c r="G4">
-        <v>-13.90130064290227</v>
+        <v>-14.40555160158056</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.558532484403853</v>
       </c>
       <c r="E5">
-        <v>-8.118745864639628</v>
+        <v>-12.50364823643505</v>
       </c>
       <c r="F5">
-        <v>1.899049519385818</v>
+        <v>0.6125932861033798</v>
       </c>
       <c r="G5">
-        <v>-13.04767984304121</v>
+        <v>-14.43665340189449</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.073211499760523</v>
       </c>
       <c r="E6">
-        <v>-8.480897585742028</v>
+        <v>-13.1978159772669</v>
       </c>
       <c r="F6">
-        <v>1.817635914303877</v>
+        <v>1.144408472170274</v>
       </c>
       <c r="G6">
-        <v>-12.4963153874717</v>
+        <v>-13.978321524457</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.526184134593342</v>
       </c>
       <c r="E7">
-        <v>-7.244694234906811</v>
+        <v>-13.21855711462309</v>
       </c>
       <c r="F7">
-        <v>2.172891215403278</v>
+        <v>0.8185850648923385</v>
       </c>
       <c r="G7">
-        <v>-13.28220564040551</v>
+        <v>-13.82155022787754</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.896027736333417</v>
       </c>
       <c r="E8">
-        <v>-7.318438655190468</v>
+        <v>-13.99876278126008</v>
       </c>
       <c r="F8">
-        <v>1.692820827519658</v>
+        <v>1.309304944106349</v>
       </c>
       <c r="G8">
-        <v>-12.43956693766697</v>
+        <v>-13.48370290794764</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.16959036689568</v>
       </c>
       <c r="E9">
-        <v>-8.701952258506026</v>
+        <v>-13.63297284703713</v>
       </c>
       <c r="F9">
-        <v>1.796273975720483</v>
+        <v>1.142822976961315</v>
       </c>
       <c r="G9">
-        <v>-11.26422799795991</v>
+        <v>-13.26743535288129</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.335393238986003</v>
       </c>
       <c r="E10">
-        <v>-7.720386447207374</v>
+        <v>-14.58084365485745</v>
       </c>
       <c r="F10">
-        <v>2.758838554508314</v>
+        <v>1.672643454322268</v>
       </c>
       <c r="G10">
-        <v>-11.59641000212709</v>
+        <v>-12.92968854661815</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.392391796202378</v>
       </c>
       <c r="E11">
-        <v>-10.04355580634274</v>
+        <v>-16.08585530226954</v>
       </c>
       <c r="F11">
-        <v>2.793364907856998</v>
+        <v>1.445889474949543</v>
       </c>
       <c r="G11">
-        <v>-11.20830976493515</v>
+        <v>-12.17875616375934</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.350875669976235</v>
       </c>
       <c r="E12">
-        <v>-12.26739696343351</v>
+        <v>-15.98894842242732</v>
       </c>
       <c r="F12">
-        <v>3.281134142382236</v>
+        <v>1.871050701171194</v>
       </c>
       <c r="G12">
-        <v>-10.4104453319342</v>
+        <v>-11.73781445604327</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.221187726271306</v>
       </c>
       <c r="E13">
-        <v>-13.16531294543879</v>
+        <v>-16.48759128050888</v>
       </c>
       <c r="F13">
-        <v>2.925227744504234</v>
+        <v>2.100317947244013</v>
       </c>
       <c r="G13">
-        <v>-9.483790257509039</v>
+        <v>-12.22804310552268</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.028605619886226</v>
       </c>
       <c r="E14">
-        <v>-13.42814477091924</v>
+        <v>-16.74663122404976</v>
       </c>
       <c r="F14">
-        <v>4.038283486093457</v>
+        <v>2.204642537952583</v>
       </c>
       <c r="G14">
-        <v>-8.621248543380146</v>
+        <v>-11.23666636731152</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.788631315738868</v>
       </c>
       <c r="E15">
-        <v>-12.8774497153036</v>
+        <v>-17.54427622503971</v>
       </c>
       <c r="F15">
-        <v>3.691860238242703</v>
+        <v>2.373168915847726</v>
       </c>
       <c r="G15">
-        <v>-9.545681874158266</v>
+        <v>-10.854552567467</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.521265968692973</v>
       </c>
       <c r="E16">
-        <v>-14.0442819773802</v>
+        <v>-17.94031815055271</v>
       </c>
       <c r="F16">
-        <v>4.11382396628955</v>
+        <v>2.655532855705188</v>
       </c>
       <c r="G16">
-        <v>-9.032927720346731</v>
+        <v>-10.69219036134567</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.240832455200111</v>
       </c>
       <c r="E17">
-        <v>-14.69451704881801</v>
+        <v>-18.38478652011321</v>
       </c>
       <c r="F17">
-        <v>3.918528067405538</v>
+        <v>2.672436520926714</v>
       </c>
       <c r="G17">
-        <v>-8.306155167934092</v>
+        <v>-10.08533975098123</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.952015814672392</v>
       </c>
       <c r="E18">
-        <v>-14.77539253294639</v>
+        <v>-18.66238716506475</v>
       </c>
       <c r="F18">
-        <v>4.80849121354241</v>
+        <v>3.341417751753567</v>
       </c>
       <c r="G18">
-        <v>-7.722773846071464</v>
+        <v>-10.05832115520779</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.665109975981483</v>
       </c>
       <c r="E19">
-        <v>-15.55441038114448</v>
+        <v>-20.03383984269301</v>
       </c>
       <c r="F19">
-        <v>4.39333500881177</v>
+        <v>3.46666027611763</v>
       </c>
       <c r="G19">
-        <v>-7.328313835055566</v>
+        <v>-9.663865060308783</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.375386966726906</v>
       </c>
       <c r="E20">
-        <v>-17.48446582875086</v>
+        <v>-20.4972427026834</v>
       </c>
       <c r="F20">
-        <v>4.60728408487202</v>
+        <v>3.389607197044026</v>
       </c>
       <c r="G20">
-        <v>-7.509658765098886</v>
+        <v>-9.340994276725803</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.086657829002875</v>
       </c>
       <c r="E21">
-        <v>-17.6700146978989</v>
+        <v>-20.79277276092423</v>
       </c>
       <c r="F21">
-        <v>4.482162502148767</v>
+        <v>3.872167657340461</v>
       </c>
       <c r="G21">
-        <v>-7.213676040059782</v>
+        <v>-8.242744097932837</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.79891078985558</v>
       </c>
       <c r="E22">
-        <v>-18.91322036302777</v>
+        <v>-21.63157608614322</v>
       </c>
       <c r="F22">
-        <v>4.804385824694135</v>
+        <v>3.75940365953217</v>
       </c>
       <c r="G22">
-        <v>-6.760732739458356</v>
+        <v>-8.703010537112336</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.511275079249416</v>
       </c>
       <c r="E23">
-        <v>-18.90495547249136</v>
+        <v>-21.26694074466858</v>
       </c>
       <c r="F23">
-        <v>4.947535995571918</v>
+        <v>3.788525743944989</v>
       </c>
       <c r="G23">
-        <v>-6.692566198184387</v>
+        <v>-8.414067684863168</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.23532773589075</v>
       </c>
       <c r="E24">
-        <v>-18.68851086429792</v>
+        <v>-22.15436571486734</v>
       </c>
       <c r="F24">
-        <v>4.924038525824106</v>
+        <v>3.766196272235126</v>
       </c>
       <c r="G24">
-        <v>-6.899334559055969</v>
+        <v>-7.9322286631273</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.973011118938858</v>
       </c>
       <c r="E25">
-        <v>-18.91330342725427</v>
+        <v>-22.14633755737645</v>
       </c>
       <c r="F25">
-        <v>5.242678330984964</v>
+        <v>4.139576252107781</v>
       </c>
       <c r="G25">
-        <v>-6.654175198972067</v>
+        <v>-8.479777515476899</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.739343403843208</v>
       </c>
       <c r="E26">
-        <v>-19.02189329055323</v>
+        <v>-21.63175467423019</v>
       </c>
       <c r="F26">
-        <v>6.101297711334708</v>
+        <v>4.126261074475181</v>
       </c>
       <c r="G26">
-        <v>-6.403240871852622</v>
+        <v>-8.334924267955865</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.543022570632226</v>
       </c>
       <c r="E27">
-        <v>-19.95661918453047</v>
+        <v>-21.99151414560949</v>
       </c>
       <c r="F27">
-        <v>5.216733863929284</v>
+        <v>4.245295813522665</v>
       </c>
       <c r="G27">
-        <v>-6.532522333259961</v>
+        <v>-8.405071059002191</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.390940603248072</v>
       </c>
       <c r="E28">
-        <v>-19.37003622985699</v>
+        <v>-23.05061210592004</v>
       </c>
       <c r="F28">
-        <v>5.408724576876126</v>
+        <v>3.909715894974557</v>
       </c>
       <c r="G28">
-        <v>-6.199936969053448</v>
+        <v>-8.380437378412742</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.294759625652299</v>
       </c>
       <c r="E29">
-        <v>-18.66045592179871</v>
+        <v>-23.06565919054989</v>
       </c>
       <c r="F29">
-        <v>5.15122988318551</v>
+        <v>3.986122847473978</v>
       </c>
       <c r="G29">
-        <v>-7.255677699041613</v>
+        <v>-8.634770894989817</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.252109264800684</v>
       </c>
       <c r="E30">
-        <v>-21.0877919741721</v>
+        <v>-22.38528426452781</v>
       </c>
       <c r="F30">
-        <v>5.336454491186285</v>
+        <v>3.870399921302887</v>
       </c>
       <c r="G30">
-        <v>-7.337579367609427</v>
+        <v>-7.998927965941062</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.270215809991929</v>
       </c>
       <c r="E31">
-        <v>-19.10829669895497</v>
+        <v>-22.23716413583912</v>
       </c>
       <c r="F31">
-        <v>5.52010188765213</v>
+        <v>3.730379322472881</v>
       </c>
       <c r="G31">
-        <v>-7.765858964058606</v>
+        <v>-8.274317137645465</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.344847241323338</v>
       </c>
       <c r="E32">
-        <v>-18.83603708376716</v>
+        <v>-21.1186212618363</v>
       </c>
       <c r="F32">
-        <v>4.593347631687322</v>
+        <v>3.953352633019229</v>
       </c>
       <c r="G32">
-        <v>-6.481680693092621</v>
+        <v>-8.473804131852431</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.469990662404345</v>
       </c>
       <c r="E33">
-        <v>-19.6881971366068</v>
+        <v>-22.2570164859718</v>
       </c>
       <c r="F33">
-        <v>4.536167086606877</v>
+        <v>3.723528724051729</v>
       </c>
       <c r="G33">
-        <v>-7.013588574596859</v>
+        <v>-8.238915440989969</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.641379958610653</v>
       </c>
       <c r="E34">
-        <v>-18.0223316145841</v>
+        <v>-20.71055994274925</v>
       </c>
       <c r="F34">
-        <v>5.25966151947716</v>
+        <v>3.852687769496228</v>
       </c>
       <c r="G34">
-        <v>-6.644162993465147</v>
+        <v>-8.003563342962584</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.842762749678584</v>
       </c>
       <c r="E35">
-        <v>-18.38870715160385</v>
+        <v>-20.66116995367438</v>
       </c>
       <c r="F35">
-        <v>4.972890665036805</v>
+        <v>3.930438333922989</v>
       </c>
       <c r="G35">
-        <v>-6.683130967232104</v>
+        <v>-8.097924790091486</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.068202455292838</v>
       </c>
       <c r="E36">
-        <v>-17.26805859945934</v>
+        <v>-20.89811481296718</v>
       </c>
       <c r="F36">
-        <v>4.920430157417512</v>
+        <v>3.50218564055409</v>
       </c>
       <c r="G36">
-        <v>-6.174555310138645</v>
+        <v>-8.551993321611683</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.303008715006782</v>
       </c>
       <c r="E37">
-        <v>-15.94121971788239</v>
+        <v>-20.15720267867439</v>
       </c>
       <c r="F37">
-        <v>5.480731241731875</v>
+        <v>3.986507209948877</v>
       </c>
       <c r="G37">
-        <v>-5.91201100182252</v>
+        <v>-8.114999059717368</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.536569523215231</v>
       </c>
       <c r="E38">
-        <v>-16.74303869625379</v>
+        <v>-20.83980787917791</v>
       </c>
       <c r="F38">
-        <v>5.322826190675428</v>
+        <v>4.05849730745657</v>
       </c>
       <c r="G38">
-        <v>-7.169019253828789</v>
+        <v>-7.827164468547128</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.762074037620855</v>
       </c>
       <c r="E39">
-        <v>-14.97958101452027</v>
+        <v>-19.60013244367514</v>
       </c>
       <c r="F39">
-        <v>4.64872730603408</v>
+        <v>4.038682759181606</v>
       </c>
       <c r="G39">
-        <v>-7.444721714884126</v>
+        <v>-8.085233960634085</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.967019628985005</v>
       </c>
       <c r="E40">
-        <v>-15.46232537965039</v>
+        <v>-18.43788948011247</v>
       </c>
       <c r="F40">
-        <v>5.40951318264359</v>
+        <v>3.75431417020937</v>
       </c>
       <c r="G40">
-        <v>-6.777219591551236</v>
+        <v>-8.063139229159495</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.151580127837243</v>
       </c>
       <c r="E41">
-        <v>-15.80318358629039</v>
+        <v>-18.53728828674959</v>
       </c>
       <c r="F41">
-        <v>5.323087954774713</v>
+        <v>4.13633899229764</v>
       </c>
       <c r="G41">
-        <v>-7.341790498634893</v>
+        <v>-8.175166279564165</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.309465176866546</v>
       </c>
       <c r="E42">
-        <v>-14.5410060518297</v>
+        <v>-17.54141881564823</v>
       </c>
       <c r="F42">
-        <v>5.259017049637782</v>
+        <v>4.119624194843952</v>
       </c>
       <c r="G42">
-        <v>-5.485211697556502</v>
+        <v>-8.042941203630345</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.439816522270157</v>
       </c>
       <c r="E43">
-        <v>-13.80790610803891</v>
+        <v>-18.05967729081696</v>
       </c>
       <c r="F43">
-        <v>4.963993999130738</v>
+        <v>3.927578809648526</v>
       </c>
       <c r="G43">
-        <v>-6.226644886220537</v>
+        <v>-8.430846940350254</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.543002051172555</v>
       </c>
       <c r="E44">
-        <v>-14.56779426487484</v>
+        <v>-18.32722301115109</v>
       </c>
       <c r="F44">
-        <v>4.521036127627341</v>
+        <v>3.92599994137879</v>
       </c>
       <c r="G44">
-        <v>-6.304964613209345</v>
+        <v>-8.295167849322391</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.614759448165085</v>
       </c>
       <c r="E45">
-        <v>-12.92770357233402</v>
+        <v>-16.92958018290846</v>
       </c>
       <c r="F45">
-        <v>4.936662845042771</v>
+        <v>3.860305436132372</v>
       </c>
       <c r="G45">
-        <v>-5.839293932726242</v>
+        <v>-7.990458710487491</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.662445039661561</v>
       </c>
       <c r="E46">
-        <v>-13.61287545743629</v>
+        <v>-17.3464878421174</v>
       </c>
       <c r="F46">
-        <v>4.661482507302386</v>
+        <v>3.797407499237806</v>
       </c>
       <c r="G46">
-        <v>-5.979798985130776</v>
+        <v>-8.772003379049391</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.684525880745904</v>
       </c>
       <c r="E47">
-        <v>-12.52038567807411</v>
+        <v>-15.73286556534972</v>
       </c>
       <c r="F47">
-        <v>5.436612393858773</v>
+        <v>3.682764764159965</v>
       </c>
       <c r="G47">
-        <v>-5.339346786506412</v>
+        <v>-8.743606310131852</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.686152277911387</v>
       </c>
       <c r="E48">
-        <v>-10.59509811706865</v>
+        <v>-15.76210832628784</v>
       </c>
       <c r="F48">
-        <v>5.022609276552831</v>
+        <v>3.790301763656591</v>
       </c>
       <c r="G48">
-        <v>-6.355192728397773</v>
+        <v>-8.544534424314872</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.670490112010989</v>
       </c>
       <c r="E49">
-        <v>-12.48532011485859</v>
+        <v>-15.42609691726391</v>
       </c>
       <c r="F49">
-        <v>4.546084301153193</v>
+        <v>3.57065351986508</v>
       </c>
       <c r="G49">
-        <v>-6.929415558234776</v>
+        <v>-8.575181955069951</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.634320818145529</v>
       </c>
       <c r="E50">
-        <v>-10.70423205105117</v>
+        <v>-15.38335206630877</v>
       </c>
       <c r="F50">
-        <v>4.216288043811431</v>
+        <v>3.949293632745511</v>
       </c>
       <c r="G50">
-        <v>-5.519824949345482</v>
+        <v>-8.081283904067732</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.584917404282908</v>
       </c>
       <c r="E51">
-        <v>-9.74974933080172</v>
+        <v>-14.91237790207321</v>
       </c>
       <c r="F51">
-        <v>5.080043302058532</v>
+        <v>3.611127551165864</v>
       </c>
       <c r="G51">
-        <v>-6.17534114426057</v>
+        <v>-8.437607463468941</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.520028380759507</v>
       </c>
       <c r="E52">
-        <v>-10.75267926115529</v>
+        <v>-13.84749451838718</v>
       </c>
       <c r="F52">
-        <v>4.672088923527832</v>
+        <v>3.298973862768926</v>
       </c>
       <c r="G52">
-        <v>-6.068277119323605</v>
+        <v>-8.482326907570121</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.448029002593931</v>
       </c>
       <c r="E53">
-        <v>-10.93499277868129</v>
+        <v>-13.65947864171219</v>
       </c>
       <c r="F53">
-        <v>4.321154386801432</v>
+        <v>3.486320748055673</v>
       </c>
       <c r="G53">
-        <v>-5.931750841675927</v>
+        <v>-8.355999503667627</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.373917190044446</v>
       </c>
       <c r="E54">
-        <v>-10.01328720220739</v>
+        <v>-13.56462344826443</v>
       </c>
       <c r="F54">
-        <v>4.109378946806127</v>
+        <v>3.270960133941053</v>
       </c>
       <c r="G54">
-        <v>-5.642965939474522</v>
+        <v>-7.70393471310199</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.297133037288818</v>
       </c>
       <c r="E55">
-        <v>-7.507816785179999</v>
+        <v>-12.34861716410185</v>
       </c>
       <c r="F55">
-        <v>4.158562432979945</v>
+        <v>3.411850518543998</v>
       </c>
       <c r="G55">
-        <v>-6.392795282743578</v>
+        <v>-8.324466930496159</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.224334215707915</v>
       </c>
       <c r="E56">
-        <v>-10.26011670445327</v>
+        <v>-12.47277326344628</v>
       </c>
       <c r="F56">
-        <v>3.907504154009082</v>
+        <v>3.156963525437396</v>
       </c>
       <c r="G56">
-        <v>-5.429046749167882</v>
+        <v>-8.01508978033235</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.150294799718094</v>
       </c>
       <c r="E57">
-        <v>-9.107152014990273</v>
+        <v>-12.14322425124378</v>
       </c>
       <c r="F57">
-        <v>4.069688551068392</v>
+        <v>3.283963845430199</v>
       </c>
       <c r="G57">
-        <v>-5.492545279112939</v>
+        <v>-8.52363541386301</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.079211539053536</v>
       </c>
       <c r="E58">
-        <v>-7.494555581419822</v>
+        <v>-12.15846653680591</v>
       </c>
       <c r="F58">
-        <v>4.410304943425521</v>
+        <v>2.796645242772084</v>
       </c>
       <c r="G58">
-        <v>-6.397076903873003</v>
+        <v>-8.457635790599667</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.009220844645689</v>
       </c>
       <c r="E59">
-        <v>-7.099178169718794</v>
+        <v>-11.37404536067421</v>
       </c>
       <c r="F59">
-        <v>3.84940412111153</v>
+        <v>3.239894699601265</v>
       </c>
       <c r="G59">
-        <v>-6.315598175928949</v>
+        <v>-8.5510482320697</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.936515679093237</v>
       </c>
       <c r="E60">
-        <v>-7.672670202296418</v>
+        <v>-11.94395317187851</v>
       </c>
       <c r="F60">
-        <v>4.065033126264659</v>
+        <v>3.059023990669604</v>
       </c>
       <c r="G60">
-        <v>-6.558217281525698</v>
+        <v>-8.336819668529012</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.863469335945</v>
       </c>
       <c r="E61">
-        <v>-7.65361942194943</v>
+        <v>-11.9515120164897</v>
       </c>
       <c r="F61">
-        <v>4.440209006666582</v>
+        <v>2.945307370348094</v>
       </c>
       <c r="G61">
-        <v>-6.802475934725666</v>
+        <v>-9.012484284826018</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.782089222621057</v>
       </c>
       <c r="E62">
-        <v>-7.918228821876906</v>
+        <v>-11.10629197977384</v>
       </c>
       <c r="F62">
-        <v>3.838965035101451</v>
+        <v>2.90148673474</v>
       </c>
       <c r="G62">
-        <v>-6.478947243505726</v>
+        <v>-9.050873978666043</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.693935173290602</v>
       </c>
       <c r="E63">
-        <v>-6.658447690350639</v>
+        <v>-11.11402525926067</v>
       </c>
       <c r="F63">
-        <v>4.554268571092853</v>
+        <v>2.967780977986044</v>
       </c>
       <c r="G63">
-        <v>-7.019172957277251</v>
+        <v>-8.818289269905238</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.594502450670774</v>
       </c>
       <c r="E64">
-        <v>-6.65502544421898</v>
+        <v>-11.28784961283872</v>
       </c>
       <c r="F64">
-        <v>3.687708460819873</v>
+        <v>3.203711611446983</v>
       </c>
       <c r="G64">
-        <v>-6.72378548200492</v>
+        <v>-8.892818195747749</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.480316643178589</v>
       </c>
       <c r="E65">
-        <v>-7.750015456798701</v>
+        <v>-10.40835727627038</v>
       </c>
       <c r="F65">
-        <v>3.889763837710728</v>
+        <v>2.603342395859208</v>
       </c>
       <c r="G65">
-        <v>-5.810207627236649</v>
+        <v>-9.043134426325688</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.352709459860219</v>
       </c>
       <c r="E66">
-        <v>-5.899888561138654</v>
+        <v>-10.90132684768223</v>
       </c>
       <c r="F66">
-        <v>3.651351415511002</v>
+        <v>2.613302685510469</v>
       </c>
       <c r="G66">
-        <v>-6.71937593439053</v>
+        <v>-8.63422655474257</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.206371886739088</v>
       </c>
       <c r="E67">
-        <v>-7.118316167503604</v>
+        <v>-10.4012677445389</v>
       </c>
       <c r="F67">
-        <v>3.760238653874192</v>
+        <v>2.434970094300986</v>
       </c>
       <c r="G67">
-        <v>-6.656206358263953</v>
+        <v>-8.592814924038331</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.044939983740061</v>
       </c>
       <c r="E68">
-        <v>-6.934910355399175</v>
+        <v>-10.28897321673818</v>
       </c>
       <c r="F68">
-        <v>3.41003142372745</v>
+        <v>2.743137678755653</v>
       </c>
       <c r="G68">
-        <v>-6.601252795365609</v>
+        <v>-9.302000195512935</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.86724558571244</v>
       </c>
       <c r="E69">
-        <v>-5.598029008838791</v>
+        <v>-10.99248983626222</v>
       </c>
       <c r="F69">
-        <v>3.466469751614986</v>
+        <v>2.454761448288671</v>
       </c>
       <c r="G69">
-        <v>-7.055906133674215</v>
+        <v>-9.045762140756644</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.675064633600107</v>
       </c>
       <c r="E70">
-        <v>-5.252531665148955</v>
+        <v>-11.2072357810238</v>
       </c>
       <c r="F70">
-        <v>4.083600153231007</v>
+        <v>2.375922409094632</v>
       </c>
       <c r="G70">
-        <v>-6.392985867098729</v>
+        <v>-8.766629161308584</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.473235649997742</v>
       </c>
       <c r="E71">
-        <v>-6.61009185089566</v>
+        <v>-9.72141612314374</v>
       </c>
       <c r="F71">
-        <v>4.089725101807306</v>
+        <v>2.327100091108434</v>
       </c>
       <c r="G71">
-        <v>-6.767110788494445</v>
+        <v>-8.879724006251021</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.262236594735641</v>
       </c>
       <c r="E72">
-        <v>-5.899560457443993</v>
+        <v>-10.20631185174012</v>
       </c>
       <c r="F72">
-        <v>3.361286972277116</v>
+        <v>2.311917773349925</v>
       </c>
       <c r="G72">
-        <v>-6.840310845340079</v>
+        <v>-9.057750679919035</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.049295764301105</v>
       </c>
       <c r="E73">
-        <v>-5.548962970247267</v>
+        <v>-11.17543048869826</v>
       </c>
       <c r="F73">
-        <v>3.60114572396213</v>
+        <v>2.482180409321335</v>
       </c>
       <c r="G73">
-        <v>-6.93024577501475</v>
+        <v>-8.639314895950649</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.835993693333469</v>
       </c>
       <c r="E74">
-        <v>-7.494318848374307</v>
+        <v>-11.36859219420471</v>
       </c>
       <c r="F74">
-        <v>2.887397861953186</v>
+        <v>2.219751959379646</v>
       </c>
       <c r="G74">
-        <v>-6.475615933407465</v>
+        <v>-8.37399275538958</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.625731643084598</v>
       </c>
       <c r="E75">
-        <v>-7.910213124019987</v>
+        <v>-11.8315091284701</v>
       </c>
       <c r="F75">
-        <v>3.317075347254901</v>
+        <v>2.094968350556734</v>
       </c>
       <c r="G75">
-        <v>-5.522989171789911</v>
+        <v>-8.546569499723645</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.422030690478582</v>
       </c>
       <c r="E76">
-        <v>-7.990170748445586</v>
+        <v>-11.36593413895682</v>
       </c>
       <c r="F76">
-        <v>3.325902430299132</v>
+        <v>2.10301842497714</v>
       </c>
       <c r="G76">
-        <v>-5.781233583764473</v>
+        <v>-8.218052980962383</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.224472666179678</v>
       </c>
       <c r="E77">
-        <v>-8.288088903198187</v>
+        <v>-11.93229926090104</v>
       </c>
       <c r="F77">
-        <v>2.234793454679679</v>
+        <v>1.643277829893026</v>
       </c>
       <c r="G77">
-        <v>-6.230480070024883</v>
+        <v>-8.339168033288718</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.03745439584248</v>
       </c>
       <c r="E78">
-        <v>-7.231943876139588</v>
+        <v>-13.10833919248479</v>
       </c>
       <c r="F78">
-        <v>3.367703506179201</v>
+        <v>2.035360688986088</v>
       </c>
       <c r="G78">
-        <v>-6.489024717627423</v>
+        <v>-7.805077569306309</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.860247410668425</v>
       </c>
       <c r="E79">
-        <v>-8.501734246958693</v>
+        <v>-12.3196526683225</v>
       </c>
       <c r="F79">
-        <v>3.010907441710593</v>
+        <v>1.73876539714853</v>
       </c>
       <c r="G79">
-        <v>-5.298287606321973</v>
+        <v>-8.065990162252989</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.6946648277533014</v>
       </c>
       <c r="E80">
-        <v>-10.18550010979141</v>
+        <v>-13.95735526435154</v>
       </c>
       <c r="F80">
-        <v>2.574627868208565</v>
+        <v>1.385786449672022</v>
       </c>
       <c r="G80">
-        <v>-4.108934189649814</v>
+        <v>-6.907292108569682</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.5424414890929656</v>
       </c>
       <c r="E81">
-        <v>-11.77144123307911</v>
+        <v>-13.54215872820843</v>
       </c>
       <c r="F81">
-        <v>2.781928467493948</v>
+        <v>1.641824873468515</v>
       </c>
       <c r="G81">
-        <v>-5.200974712432816</v>
+        <v>-6.941934078549164</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4034232079425296</v>
       </c>
       <c r="E82">
-        <v>-12.62532902182988</v>
+        <v>-15.01229170691462</v>
       </c>
       <c r="F82">
-        <v>2.30071658932927</v>
+        <v>1.373705539469594</v>
       </c>
       <c r="G82">
-        <v>-4.234148110984198</v>
+        <v>-7.008821354973486</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.2820680967940501</v>
       </c>
       <c r="E83">
-        <v>-13.19645787716368</v>
+        <v>-16.10786316907981</v>
       </c>
       <c r="F83">
-        <v>2.263499698656294</v>
+        <v>1.426185927906553</v>
       </c>
       <c r="G83">
-        <v>-4.298304548566215</v>
+        <v>-7.247007416254525</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.179362954161547</v>
       </c>
       <c r="E84">
-        <v>-12.74650311544308</v>
+        <v>-16.07192127827474</v>
       </c>
       <c r="F84">
-        <v>2.499004551272193</v>
+        <v>1.405103977505306</v>
       </c>
       <c r="G84">
-        <v>-5.422331914079538</v>
+        <v>-6.960969017362971</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.09911709016141179</v>
       </c>
       <c r="E85">
-        <v>-13.60016247757099</v>
+        <v>-17.19648215548724</v>
       </c>
       <c r="F85">
-        <v>2.68726264070202</v>
+        <v>1.287447641816081</v>
       </c>
       <c r="G85">
-        <v>-3.75289650678133</v>
+        <v>-6.808083814107377</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.04420906847976008</v>
       </c>
       <c r="E86">
-        <v>-15.43050762769087</v>
+        <v>-18.99412076642411</v>
       </c>
       <c r="F86">
-        <v>2.356111174289278</v>
+        <v>1.04390265518861</v>
       </c>
       <c r="G86">
-        <v>-4.516821260097807</v>
+        <v>-6.409987035876059</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.0161413617833155</v>
       </c>
       <c r="E87">
-        <v>-17.27836686996756</v>
+        <v>-19.84307038690966</v>
       </c>
       <c r="F87">
-        <v>1.660236167363137</v>
+        <v>1.000255976735104</v>
       </c>
       <c r="G87">
-        <v>-5.96015574282724</v>
+        <v>-6.674431966254515</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.01994236873760242</v>
       </c>
       <c r="E88">
-        <v>-18.28626819427695</v>
+        <v>-21.19833384679373</v>
       </c>
       <c r="F88">
-        <v>1.408183847508915</v>
+        <v>1.189287761319145</v>
       </c>
       <c r="G88">
-        <v>-4.313339826666437</v>
+        <v>-5.977895752323855</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.0567264415052401</v>
       </c>
       <c r="E89">
-        <v>-18.79736237991035</v>
+        <v>-21.46289340818531</v>
       </c>
       <c r="F89">
-        <v>1.494445058632038</v>
+        <v>0.6590481300523762</v>
       </c>
       <c r="G89">
-        <v>-3.830558326133177</v>
+        <v>-6.392241804890262</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.1306885501234679</v>
       </c>
       <c r="E90">
-        <v>-21.83811528532695</v>
+        <v>-23.49089819167644</v>
       </c>
       <c r="F90">
-        <v>2.087242996158226</v>
+        <v>1.059520694200992</v>
       </c>
       <c r="G90">
-        <v>-3.737451341780304</v>
+        <v>-5.76842266005588</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2427594985490663</v>
       </c>
       <c r="E91">
-        <v>-23.89094381290657</v>
+        <v>-25.91523977868463</v>
       </c>
       <c r="F91">
-        <v>1.86345954229194</v>
+        <v>0.5868807619204832</v>
       </c>
       <c r="G91">
-        <v>-4.141526725125272</v>
+        <v>-6.243606893829</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3914443027369765</v>
       </c>
       <c r="E92">
-        <v>-23.80665854228051</v>
+        <v>-27.12133234741484</v>
       </c>
       <c r="F92">
-        <v>1.36682180635233</v>
+        <v>0.5594974206861399</v>
       </c>
       <c r="G92">
-        <v>-4.171667771429674</v>
+        <v>-5.662554356141645</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5766531046518847</v>
       </c>
       <c r="E93">
-        <v>-27.9948232936188</v>
+        <v>-28.58080403265019</v>
       </c>
       <c r="F93">
-        <v>2.209935805656472</v>
+        <v>0.5333384064731344</v>
       </c>
       <c r="G93">
-        <v>-3.870286026576148</v>
+        <v>-5.891284300513671</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7918493935474136</v>
       </c>
       <c r="E94">
-        <v>-28.99920684793606</v>
+        <v>-30.71647666652617</v>
       </c>
       <c r="F94">
-        <v>1.522326248675464</v>
+        <v>0.2749706135399685</v>
       </c>
       <c r="G94">
-        <v>-5.239245617393946</v>
+        <v>-6.123074037546482</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.033581461957089</v>
       </c>
       <c r="E95">
-        <v>-32.31967022965721</v>
+        <v>-32.87742574452506</v>
       </c>
       <c r="F95">
-        <v>1.446833813788734</v>
+        <v>0.1554007491502767</v>
       </c>
       <c r="G95">
-        <v>-4.415641853469211</v>
+        <v>-5.956482425187543</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.296205027047553</v>
       </c>
       <c r="E96">
-        <v>-34.67063287897833</v>
+        <v>-34.82208180654386</v>
       </c>
       <c r="F96">
-        <v>1.623025903629383</v>
+        <v>0.1155281125839253</v>
       </c>
       <c r="G96">
-        <v>-4.472720562464721</v>
+        <v>-6.083985969528334</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.570382169641434</v>
       </c>
       <c r="E97">
-        <v>-37.26915807234416</v>
+        <v>-37.691325773696</v>
       </c>
       <c r="F97">
-        <v>0.8834213815094558</v>
+        <v>0.1279801313828075</v>
       </c>
       <c r="G97">
-        <v>-4.446057027955681</v>
+        <v>-6.397849684271973</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.853518864506054</v>
       </c>
       <c r="E98">
-        <v>-39.4023636986932</v>
+        <v>-38.83099603370822</v>
       </c>
       <c r="F98">
-        <v>1.207246766611838</v>
+        <v>-0.7038365932819552</v>
       </c>
       <c r="G98">
-        <v>-5.238389293168061</v>
+        <v>-6.771569940256067</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.128997296140382</v>
       </c>
       <c r="E99">
-        <v>-40.57801530501808</v>
+        <v>-41.10257004855524</v>
       </c>
       <c r="F99">
-        <v>0.2686485135218027</v>
+        <v>-0.1459386028031135</v>
       </c>
       <c r="G99">
-        <v>-4.705854832961955</v>
+        <v>-6.342723812230616</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.397788387791135</v>
       </c>
       <c r="E100">
-        <v>-42.66948531076391</v>
+        <v>-44.10830307608089</v>
       </c>
       <c r="F100">
-        <v>0.79059950055616</v>
+        <v>-0.4262440496646185</v>
       </c>
       <c r="G100">
-        <v>-5.069521111525671</v>
+        <v>-6.522269939250659</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.634465275764578</v>
       </c>
       <c r="E101">
-        <v>-45.67416757582436</v>
+        <v>-45.74222105829018</v>
       </c>
       <c r="F101">
-        <v>0.1446046367895907</v>
+        <v>-0.5970376691412235</v>
       </c>
       <c r="G101">
-        <v>-5.467077465626629</v>
+        <v>-6.580178865026143</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.850999108800071</v>
       </c>
       <c r="E102">
-        <v>-50.02321527425255</v>
+        <v>-48.18988292688728</v>
       </c>
       <c r="F102">
-        <v>0.3194613983769272</v>
+        <v>-0.5729893350705509</v>
       </c>
       <c r="G102">
-        <v>-5.241224561794009</v>
+        <v>-7.017329771595925</v>
       </c>
     </row>
   </sheetData>
